--- a/docs/CodeSystem-BRImunobiologico.xlsx
+++ b/docs/CodeSystem-BRImunobiologico.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="398">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -43,7 +43,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Imunobiológico</t>
+    <t>Imunobiológico (CodeSystem)</t>
   </si>
   <si>
     <t>Status</t>
@@ -73,7 +73,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>null (http://www.saude.gov.br)</t>
+    <t>Ministério da Saúde do Brasil (http://www.saude.gov.br, cgiis.datasus@saude.gov.br)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -133,12 +133,27 @@
     <t>Type</t>
   </si>
   <si>
+    <t>Nome técnico completo e oficial do produto, conforme registro junto aos órgãos competentes.</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Classificação ampla do produto, limitada às categorias: Anticorpo Monoclonal, Diluente, Imunoglobulina, Soro e Vacina.</t>
+  </si>
+  <si>
     <t>inactive</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/concept-properties#inactive</t>
   </si>
   <si>
+    <t>Status do imunobiológico em que determina se ele está apto para uso no registro de doses aplicadas. Serão aceitos códigos inativos apenas em caso de Transcrição de Caderneta.</t>
+  </si>
+  <si>
     <t>boolean</t>
   </si>
   <si>
@@ -154,10 +169,10 @@
     <t>1</t>
   </si>
   <si>
-    <t>IGHT</t>
-  </si>
-  <si>
-    <t>Imunoglobulina humana antitétano</t>
+    <t>IGHAT</t>
+  </si>
+  <si>
+    <t>imunoglobulina humana antitétano</t>
   </si>
   <si>
     <t>2</t>
@@ -166,25 +181,25 @@
     <t>SAT</t>
   </si>
   <si>
-    <t>Soro antitetânico</t>
+    <t>soro antitetânico</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>SARC</t>
-  </si>
-  <si>
-    <t>Soro antiaracnídico</t>
+    <t>SAAR</t>
+  </si>
+  <si>
+    <t>soro antiaracnídico (Loxosceles, Phoneutria, Tityus)</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>SAESCOR</t>
-  </si>
-  <si>
-    <t>Soro antiescorpiônico</t>
+    <t>SAESC</t>
+  </si>
+  <si>
+    <t>soro antiescorpiônico</t>
   </si>
   <si>
     <t>5</t>
@@ -193,16 +208,16 @@
     <t>DT</t>
   </si>
   <si>
-    <t>Vacina difteria e tétano infantil</t>
+    <t>vacina difteria e tétano infantil</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>SAELAP</t>
-  </si>
-  <si>
-    <t>Soro antielapídico</t>
+    <t>SAELA</t>
+  </si>
+  <si>
+    <t>soro antielapídico</t>
   </si>
   <si>
     <t>7</t>
@@ -211,25 +226,25 @@
     <t>SAR</t>
   </si>
   <si>
-    <t>Soro antirrábico</t>
+    <t>soro antirrábico</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>SABOTR</t>
-  </si>
-  <si>
-    <t>Soro antibotrópico (pentavalente)</t>
+    <t>SABR</t>
+  </si>
+  <si>
+    <t>soro antibotrópico</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
-    <t>HepB</t>
-  </si>
-  <si>
-    <t>Vacina hepatite B</t>
+    <t>HB</t>
+  </si>
+  <si>
+    <t>vacina hepatite B</t>
   </si>
   <si>
     <t>10</t>
@@ -238,34 +253,34 @@
     <t>SAD</t>
   </si>
   <si>
-    <t>Soro antidiftérico</t>
+    <t>soro antidiftérico</t>
   </si>
   <si>
     <t>11</t>
   </si>
   <si>
-    <t>SABOCR</t>
-  </si>
-  <si>
-    <t>Soro antibotrópico (pentavalente) e anticrotálico</t>
+    <t>SABC</t>
+  </si>
+  <si>
+    <t>soro antibotrópico e anticrotálico</t>
   </si>
   <si>
     <t>12</t>
   </si>
   <si>
-    <t>SABOLA</t>
-  </si>
-  <si>
-    <t>Soro antibotrópico (pentavalente) e antilaquético</t>
+    <t>SABL</t>
+  </si>
+  <si>
+    <t>soro antibotrópico e antilaquético</t>
   </si>
   <si>
     <t>13</t>
   </si>
   <si>
-    <t>Meningo AC</t>
-  </si>
-  <si>
-    <t>Vacina meningocócica AC</t>
+    <t>MenAC</t>
+  </si>
+  <si>
+    <t>vacina meningo AC</t>
   </si>
   <si>
     <t>14</t>
@@ -274,7 +289,7 @@
     <t>VFA</t>
   </si>
   <si>
-    <t>Vacina febre amarela</t>
+    <t>vacina febre amarela</t>
   </si>
   <si>
     <t>15</t>
@@ -283,16 +298,16 @@
     <t>BCG</t>
   </si>
   <si>
-    <t>Vacina BCG</t>
+    <t>vacina BCG</t>
   </si>
   <si>
     <t>16</t>
   </si>
   <si>
-    <t>SACROT</t>
-  </si>
-  <si>
-    <t>Soro anticrotálico</t>
+    <t>SAC</t>
+  </si>
+  <si>
+    <t>soro anticrotálico</t>
   </si>
   <si>
     <t>17</t>
@@ -301,187 +316,187 @@
     <t>Hib</t>
   </si>
   <si>
-    <t>Vacina Hib</t>
+    <t>vacina Hib</t>
   </si>
   <si>
     <t>18</t>
   </si>
   <si>
+    <t>VR embrião de galinha</t>
+  </si>
+  <si>
+    <t>vacina raiva embrião de galinha</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>IGHAVZ</t>
+  </si>
+  <si>
+    <t>imunoglobulina humana antivaricela</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>IGHAHB</t>
+  </si>
+  <si>
+    <t>imunoglobulina humana anti-hepatite B</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>VPP23</t>
+  </si>
+  <si>
+    <t>vacina pneumo 23</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>VIP</t>
+  </si>
+  <si>
+    <t>vacina inativada poliomielite</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>IGHAR</t>
+  </si>
+  <si>
+    <t>imunoglobulina humana antirrábica</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>SCR</t>
+  </si>
+  <si>
+    <t>vacina tríplice viral</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>dT</t>
+  </si>
+  <si>
+    <t>vacina difteria e tétano adulto</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>VPC10</t>
+  </si>
+  <si>
+    <t>vacina pneumo 10</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>SALATRO</t>
+  </si>
+  <si>
+    <t>soro antilatrodéctico</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>VOPb</t>
+  </si>
+  <si>
+    <t>vacina oral poliomielite bivalente</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>Penta acelular</t>
+  </si>
+  <si>
+    <t>vacina penta acelular (DTPa/VIP/Hib)</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>FTp</t>
+  </si>
+  <si>
+    <t>vacina febre tifóide</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>SALOX</t>
+  </si>
+  <si>
+    <t>soro antiloxoscélico</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>SALON</t>
+  </si>
+  <si>
+    <t>soro antilonômico</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>INF3</t>
+  </si>
+  <si>
+    <t>vacina influenza trivalente</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>VZ</t>
+  </si>
+  <si>
+    <t>vacina varicela</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>HA virossomal</t>
+  </si>
+  <si>
+    <t>vacina hepatite A (virossomal)</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>SR</t>
+  </si>
+  <si>
+    <t>vacina dupla viral</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
     <t>VR</t>
   </si>
   <si>
-    <t>Vacina raiva embrião de galinha</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>IGHV</t>
-  </si>
-  <si>
-    <t>Imunoglobulina humana antivaricela</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>IGHHB</t>
-  </si>
-  <si>
-    <t>Imunoglobulina humana anti-hepatite B</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>VPP23</t>
-  </si>
-  <si>
-    <t>Vacina pneumo 23</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>VIP</t>
-  </si>
-  <si>
-    <t>Vacina polio injetável</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>IGHR</t>
-  </si>
-  <si>
-    <t>Imunoglobulina humana antirrábica</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>SCR</t>
-  </si>
-  <si>
-    <t>Vacina sarampo, caxumba, rubéola</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>dT</t>
-  </si>
-  <si>
-    <t>Vacina difteria e tétano adulto</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>VPC10</t>
-  </si>
-  <si>
-    <t>Vacina pneumo 10</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>SLATRO</t>
-  </si>
-  <si>
-    <t>Soro latrodectus</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>VOP</t>
-  </si>
-  <si>
-    <t>Vacina polio oral</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>PENTA acelular</t>
-  </si>
-  <si>
-    <t>Vacina penta acelular (DTPa/VIP/Hib)</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>FTp</t>
-  </si>
-  <si>
-    <t>Vacina febre tifóide</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>SALOXO</t>
-  </si>
-  <si>
-    <t>Soro antiloxoscélico (trivalente)</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>SALONO</t>
-  </si>
-  <si>
-    <t>Soro antilonômico</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>INF3</t>
-  </si>
-  <si>
-    <t>Vacina influenza trivalente</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>VAR</t>
-  </si>
-  <si>
-    <t>Vacina varicela</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>HA</t>
-  </si>
-  <si>
-    <t>Vacina hepatite A</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>SR</t>
-  </si>
-  <si>
-    <t>Vacina sarampo, rubéola</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>Vero</t>
-  </si>
-  <si>
-    <t>Vacina raiva em cultivo celular vero</t>
+    <t>vacina raiva (inativada)</t>
   </si>
   <si>
     <t>38</t>
@@ -490,7 +505,7 @@
     <t>SBOTULTRI</t>
   </si>
   <si>
-    <t>Soro antibotulínico (trivalente)</t>
+    <t>soro antibotulínico (trivalente)</t>
   </si>
   <si>
     <t>39</t>
@@ -499,16 +514,16 @@
     <t>Tetra</t>
   </si>
   <si>
-    <t>Vacina DTP/Hib</t>
+    <t>vacina DTP/Hib</t>
   </si>
   <si>
     <t>40</t>
   </si>
   <si>
-    <t>Pncc7V</t>
-  </si>
-  <si>
-    <t>Vacina pneumocócica 7V</t>
+    <t>VPC7</t>
+  </si>
+  <si>
+    <t>vacina pneumo 7</t>
   </si>
   <si>
     <t>41</t>
@@ -517,34 +532,34 @@
     <t>MenC</t>
   </si>
   <si>
-    <t>Vacina meningo C</t>
+    <t>vacina meningo C</t>
   </si>
   <si>
     <t>42</t>
   </si>
   <si>
-    <t>PENTA</t>
-  </si>
-  <si>
-    <t>Vacina penta (DTP/HepB/Hib)</t>
+    <t>Penta</t>
+  </si>
+  <si>
+    <t>vacina penta (DTP/HB/Hib)</t>
   </si>
   <si>
     <t>43</t>
   </si>
   <si>
-    <t>HEXA</t>
-  </si>
-  <si>
-    <t>Vacina hexa (DTPa/HepB/VIP/Hib)</t>
+    <t>Hexa acelular</t>
+  </si>
+  <si>
+    <t>vacina hexa acelular (DTPa/HB/VIP/Hib)</t>
   </si>
   <si>
     <t>44</t>
   </si>
   <si>
-    <t>H1N1</t>
-  </si>
-  <si>
-    <t>Vacina Influenza H1N1</t>
+    <t>INFH1N1-2009</t>
+  </si>
+  <si>
+    <t>vacina influenza A (H1N1) (inativada, fragmentada)</t>
   </si>
   <si>
     <t>45</t>
@@ -553,7 +568,7 @@
     <t>ROTA</t>
   </si>
   <si>
-    <t>Vacina rotavírus</t>
+    <t>vacina rotavírus</t>
   </si>
   <si>
     <t>46</t>
@@ -562,7 +577,7 @@
     <t>DTP</t>
   </si>
   <si>
-    <t>Vacina DTP</t>
+    <t>vacina DTP</t>
   </si>
   <si>
     <t>47</t>
@@ -571,16 +586,16 @@
     <t>DTPa</t>
   </si>
   <si>
-    <t>Vacina DTPa infantil</t>
+    <t>vacina DTPa infantil</t>
   </si>
   <si>
     <t>48</t>
   </si>
   <si>
-    <t>DILSRC</t>
-  </si>
-  <si>
-    <t>Diluente para vacina sarampo, caxumba, rubéola</t>
+    <t>DILSCR</t>
+  </si>
+  <si>
+    <t>diluente para vacina tríplice viral</t>
   </si>
   <si>
     <t>49</t>
@@ -589,7 +604,7 @@
     <t>DILVFA</t>
   </si>
   <si>
-    <t>Diluente para vacina febre amarela</t>
+    <t>diluente para vacina febre amarela</t>
   </si>
   <si>
     <t>50</t>
@@ -598,7 +613,7 @@
     <t>DILHib</t>
   </si>
   <si>
-    <t>Diluente para vacina haemophilus influenzae B</t>
+    <t>diluente para vacina Hib</t>
   </si>
   <si>
     <t>51</t>
@@ -607,16 +622,16 @@
     <t>Fta</t>
   </si>
   <si>
-    <t>Vacina febre tifóide (atenuada)</t>
+    <t>vacina febre tifóide (atenuada)</t>
   </si>
   <si>
     <t>52</t>
   </si>
   <si>
-    <t>DilMengAC</t>
-  </si>
-  <si>
-    <t>Diluente meningo AC</t>
+    <t>DILMenAC</t>
+  </si>
+  <si>
+    <t>diluente para vacina meningo AC</t>
   </si>
   <si>
     <t>53</t>
@@ -625,7 +640,7 @@
     <t>DILSR</t>
   </si>
   <si>
-    <t>Diluente para vacina sarampo, rubéola</t>
+    <t>diluente para vacina dupla viral</t>
   </si>
   <si>
     <t>54</t>
@@ -634,16 +649,16 @@
     <t>DILVAR</t>
   </si>
   <si>
-    <t>Diluente para vacina varicela</t>
+    <t>diluente para vacina varicela</t>
   </si>
   <si>
     <t>55</t>
   </si>
   <si>
-    <t>HepAinf</t>
-  </si>
-  <si>
-    <t>Vacina hepatite A infantil</t>
+    <t>HAinf</t>
+  </si>
+  <si>
+    <t>vacina hepatite A infantil</t>
   </si>
   <si>
     <t>56</t>
@@ -652,7 +667,7 @@
     <t>SCRV</t>
   </si>
   <si>
-    <t>Vacina sarampo, caxumba, rubéola e varicela</t>
+    <t>vacina tetraviral</t>
   </si>
   <si>
     <t>57</t>
@@ -661,16 +676,16 @@
     <t>dTpa</t>
   </si>
   <si>
-    <t>Vacina dTpa adulto</t>
+    <t>vacina dTpa adulto</t>
   </si>
   <si>
     <t>58</t>
   </si>
   <si>
-    <t>TETRA acelular</t>
-  </si>
-  <si>
-    <t>Vacina DTPa/VIP</t>
+    <t>DTPa/VIP</t>
+  </si>
+  <si>
+    <t>vacina tetra acelular DTPa/VIP</t>
   </si>
   <si>
     <t>59</t>
@@ -679,7 +694,7 @@
     <t>VPC13</t>
   </si>
   <si>
-    <t>Vacina pneumo 13</t>
+    <t>vacina pneumo 13</t>
   </si>
   <si>
     <t>60</t>
@@ -688,43 +703,43 @@
     <t>HPV2</t>
   </si>
   <si>
-    <t>Vacina HPV bivalente</t>
+    <t>vacina HPV bivalente</t>
   </si>
   <si>
     <t>61</t>
   </si>
   <si>
-    <t>TT</t>
-  </si>
-  <si>
-    <t>Vacina toxóide tetânico</t>
+    <t>Tétano</t>
+  </si>
+  <si>
+    <t>vacina tétano</t>
   </si>
   <si>
     <t>62</t>
   </si>
   <si>
-    <t>HAeHBped</t>
-  </si>
-  <si>
-    <t>Hepatite AeB (pediátrica)</t>
+    <t>HA-HBinf</t>
+  </si>
+  <si>
+    <t>vacina hepatite A e B infantil</t>
   </si>
   <si>
     <t>63</t>
   </si>
   <si>
-    <t>HAeHB</t>
-  </si>
-  <si>
-    <t>Vacina hepatite AeB (uso adulto)</t>
+    <t>HA-HBad</t>
+  </si>
+  <si>
+    <t>vacina hepatite A e B adulto</t>
   </si>
   <si>
     <t>64</t>
   </si>
   <si>
-    <t>FLU ID</t>
-  </si>
-  <si>
-    <t>Vacina influenza ID</t>
+    <t>INF3-ID</t>
+  </si>
+  <si>
+    <t>vacina influenza trivalente ID</t>
   </si>
   <si>
     <t>65</t>
@@ -733,16 +748,16 @@
     <t>ROTA5</t>
   </si>
   <si>
-    <t>Vacina rotavírus pentavalente</t>
+    <t>vacina rotavírus pentavalente</t>
   </si>
   <si>
     <t>66</t>
   </si>
   <si>
-    <t>MEN BC</t>
-  </si>
-  <si>
-    <t>Vacina meningocócica B/C</t>
+    <t>MenBC</t>
+  </si>
+  <si>
+    <t>vacina meningo BC</t>
   </si>
   <si>
     <t>67</t>
@@ -751,22 +766,19 @@
     <t>HPV4</t>
   </si>
   <si>
-    <t>Vacina HPV quadrivalente</t>
+    <t>vacina HPV quadrivalente</t>
   </si>
   <si>
     <t>68</t>
   </si>
   <si>
-    <t>HPV Bi</t>
-  </si>
-  <si>
     <t>69</t>
   </si>
   <si>
-    <t>SABOT</t>
-  </si>
-  <si>
-    <t>Soro antibotulínico AB (bivalente)</t>
+    <t>SAB</t>
+  </si>
+  <si>
+    <t>soro antibotulínico AB (bivalente)</t>
   </si>
   <si>
     <t>70</t>
@@ -775,34 +787,25 @@
     <t>Sarampo</t>
   </si>
   <si>
-    <t>Vacina sarampo</t>
+    <t>vacina sarampo</t>
   </si>
   <si>
     <t>71</t>
   </si>
   <si>
-    <t>Rubeola</t>
-  </si>
-  <si>
-    <t>Vacina rubéola</t>
+    <t>Rubéola</t>
+  </si>
+  <si>
+    <t>vacina rubéola</t>
   </si>
   <si>
     <t>72</t>
   </si>
   <si>
-    <t>Gripe Sazonal</t>
-  </si>
-  <si>
-    <t>Vacina gripe</t>
-  </si>
-  <si>
     <t>73</t>
   </si>
   <si>
-    <t>Quadrupla Viral</t>
-  </si>
-  <si>
-    <t>Vacina quádrupla viral</t>
+    <t>vacina sarampo, caxumba, rubéola e varicela</t>
   </si>
   <si>
     <t>74</t>
@@ -811,16 +814,16 @@
     <t>MenACWY</t>
   </si>
   <si>
-    <t>Vacina meningo ACWY</t>
+    <t>vacina meningo ACWY</t>
   </si>
   <si>
     <t>75</t>
   </si>
   <si>
-    <t>COLERA</t>
-  </si>
-  <si>
-    <t>Vacina cólera</t>
+    <t>VCO</t>
+  </si>
+  <si>
+    <t>vacina cólera oral</t>
   </si>
   <si>
     <t>76</t>
@@ -829,7 +832,7 @@
     <t>VHZ</t>
   </si>
   <si>
-    <t>Vacina herpes-zóster</t>
+    <t>vacina herpes-zóster (atenuada)</t>
   </si>
   <si>
     <t>77</t>
@@ -838,7 +841,7 @@
     <t>INF4</t>
   </si>
   <si>
-    <t>Vacina influenza tetravalente</t>
+    <t>vacina influenza tetravalente</t>
   </si>
   <si>
     <t>78</t>
@@ -847,7 +850,7 @@
     <t>MenB</t>
   </si>
   <si>
-    <t>Vacina meningo B</t>
+    <t>vacina meningo B</t>
   </si>
   <si>
     <t>79</t>
@@ -856,16 +859,16 @@
     <t>DILBCG</t>
   </si>
   <si>
-    <t>Diluente para vacina BCG</t>
+    <t>diluente para vacina BCG</t>
   </si>
   <si>
     <t>80</t>
   </si>
   <si>
-    <t>DILVRvero</t>
-  </si>
-  <si>
-    <t>Diluente para vacina raiva cultivo celulas vero</t>
+    <t>DILVR</t>
+  </si>
+  <si>
+    <t>diluente para vacina raiva (inativada)</t>
   </si>
   <si>
     <t>81</t>
@@ -874,7 +877,7 @@
     <t>DILMenC</t>
   </si>
   <si>
-    <t>Diluente para vacina meningo C</t>
+    <t>diluente para vacina meningo C</t>
   </si>
   <si>
     <t>82</t>
@@ -883,16 +886,16 @@
     <t>Dengue</t>
   </si>
   <si>
-    <t>Vacina dengue</t>
+    <t>vacina dengue (recombinante e atenuada)</t>
   </si>
   <si>
     <t>83</t>
   </si>
   <si>
-    <t>HEPAad</t>
-  </si>
-  <si>
-    <t>Vacina hepatite A adulto</t>
+    <t>HAad</t>
+  </si>
+  <si>
+    <t>vacina hepatite A adulto</t>
   </si>
   <si>
     <t>84</t>
@@ -901,7 +904,7 @@
     <t>VFA-F</t>
   </si>
   <si>
-    <t>Vacina febre amarela fracionada</t>
+    <t>vacina febre amarela fracionada</t>
   </si>
   <si>
     <t>85</t>
@@ -910,7 +913,7 @@
     <t>COVID-19 ASTRAZENECA/FIOCRUZ - COVISHIELD</t>
   </si>
   <si>
-    <t>Vacina COVID-19 ASTRAZENECA/FIOCRUZ - COVISHIELD, recombinante</t>
+    <t>vacina covid-19-recombinante, AstraZeneca/Fiocruz (Covishield)</t>
   </si>
   <si>
     <t>86</t>
@@ -919,7 +922,7 @@
     <t>COVID-19 SINOVAC/BUTANTAN - CORONAVAC</t>
   </si>
   <si>
-    <t>Vacina COVID-19 SINOVAC/BUTANTAN - CORONAVAC, inativada</t>
+    <t>vacina covid-19-inativada, Sinovac/Butantan (Coronavac)</t>
   </si>
   <si>
     <t>87</t>
@@ -928,7 +931,7 @@
     <t>COVID-19 PFIZER - COMIRNATY</t>
   </si>
   <si>
-    <t>Vacina COVID-19 PFIZER - COMIRNATY, RNAm</t>
+    <t>vacina covid-19-RNAm, Pfizer (Comirnaty)</t>
   </si>
   <si>
     <t>88</t>
@@ -937,7 +940,7 @@
     <t>COVID-19 JANSSEN - Ad26.COV2.S</t>
   </si>
   <si>
-    <t>Vacina COVID-19 JANSSEN - Ad26.COV2.S, recombinante</t>
+    <t>vacina covid-19-recombinante, Janssen (Ad26.COV2.S)</t>
   </si>
   <si>
     <t>89</t>
@@ -946,7 +949,7 @@
     <t>COVID-19 ASTRAZENECA - ChAdOx1-S</t>
   </si>
   <si>
-    <t>Vacina COVID-19 ASTRAZENECA - ChAdOx1-S, recombinante</t>
+    <t>vacina covid-19-recombinante, AstraZeneca/Covax (ChAdOx1-S)</t>
   </si>
   <si>
     <t>90</t>
@@ -955,25 +958,22 @@
     <t>DILSCRV</t>
   </si>
   <si>
-    <t>Diluente para vacina sarampo, caxumba, rubéola e varicela</t>
+    <t>diluente para vacina tetraviral</t>
   </si>
   <si>
     <t>91</t>
   </si>
   <si>
-    <t>DILVR</t>
-  </si>
-  <si>
-    <t>Diluente para vacina raiva cultivo embrião de galinha</t>
+    <t>DILVR embrião de galinha</t>
+  </si>
+  <si>
+    <t>diluente para vacina raiva embrião de galinha</t>
   </si>
   <si>
     <t>92</t>
   </si>
   <si>
-    <t>VRvero</t>
-  </si>
-  <si>
-    <t>Vacina raiva cultivo celulas vero</t>
+    <t>vacina raiva</t>
   </si>
   <si>
     <t>93</t>
@@ -982,16 +982,16 @@
     <t>HPV9</t>
   </si>
   <si>
-    <t>Vacina HPV nonavalente</t>
+    <t>vacina HPV nonavalente</t>
   </si>
   <si>
     <t>94</t>
   </si>
   <si>
-    <t>DILCOV</t>
-  </si>
-  <si>
-    <t>Diluente COVID-19</t>
+    <t>NaCl 0,9%</t>
+  </si>
+  <si>
+    <t>cloreto de sódio, solução injetável - 0,9%</t>
   </si>
   <si>
     <t>95</t>
@@ -1000,7 +1000,7 @@
     <t>COVID-19 GAMALEYA - SPUTNIK V</t>
   </si>
   <si>
-    <t>Vacina COVID-19 GAMALEYA - SPUTNIK V recombinante</t>
+    <t>vacina covid-19-recombinante, Gamaleya (Sputnik V)</t>
   </si>
   <si>
     <t>96</t>
@@ -1009,7 +1009,7 @@
     <t>COVID-19 BHARAT - COVAXIN</t>
   </si>
   <si>
-    <t>Vacina COVID-19 BHARAT - COVAXIN inativada</t>
+    <t>vacina covid-19-inativada, Bharat (Covaxin)</t>
   </si>
   <si>
     <t>97</t>
@@ -1018,7 +1018,7 @@
     <t>COVID-19 MODERNA - SPIKEVAX</t>
   </si>
   <si>
-    <t>Vacina COVID-19-RNAm, Moderna (Spikevax)</t>
+    <t>vacina covid-19-RNAm, Moderna (Spikevax)</t>
   </si>
   <si>
     <t>98</t>
@@ -1027,7 +1027,7 @@
     <t>COVID-19 SINOVAC - CORONAVAC</t>
   </si>
   <si>
-    <t>Vacina COVID-19 SINOVAC - CORONAVAC inativada</t>
+    <t>vacina covid-19-inativada, Sinovac (Coronavac)</t>
   </si>
   <si>
     <t>99</t>
@@ -1036,25 +1036,25 @@
     <t>COVID-19 PFIZER - COMIRNATY PEDIÁTRICA</t>
   </si>
   <si>
-    <t>Vacina COVID-19 PFIZER - COMIRNATY PEDIÁTRICA, RNAm</t>
+    <t>vacina covid-19-RNAm, Pfizer (Comirnaty) pediátrica</t>
   </si>
   <si>
     <t>100</t>
   </si>
   <si>
-    <t>VVBN</t>
-  </si>
-  <si>
-    <t>Vacina Varíola Bavarian Nordic</t>
+    <t>VVS</t>
+  </si>
+  <si>
+    <t>vacina varíola símia (atenuada)</t>
   </si>
   <si>
     <t>101</t>
   </si>
   <si>
-    <t>VZR</t>
-  </si>
-  <si>
-    <t>Vacina Herpes-Zoster, recombinante</t>
+    <t>VHZR</t>
+  </si>
+  <si>
+    <t>vacina herpes-zóster (recombinante)</t>
   </si>
   <si>
     <t>102</t>
@@ -1063,7 +1063,7 @@
     <t>COVID-19 PFIZER - COMIRNATY PEDIÁTRICA MENOR DE 5 ANOS</t>
   </si>
   <si>
-    <t>Vacina COVID-19 PFIZER - COMIRNATY PEDIÁTRICA MENOR DE 5 ANOS, RNAm</t>
+    <t>vacina covid-19-RNAm, Pfizer (Comirnaty) pediátrica menor de 5 anos</t>
   </si>
   <si>
     <t>103</t>
@@ -1072,7 +1072,7 @@
     <t>COVID-19 PFIZER - COMIRNATY BIVALENTE</t>
   </si>
   <si>
-    <t>Vacina COVID-19 PFIZER - COMIRNATY BIVALENTE, RNAm</t>
+    <t>vacina covid-19-RNAm, Pfizer (Comirnaty) bivalente</t>
   </si>
   <si>
     <t>104</t>
@@ -1081,16 +1081,16 @@
     <t>DNG</t>
   </si>
   <si>
-    <t>Vacina dengue (atenuada)</t>
+    <t>vacina dengue (atenuada)</t>
   </si>
   <si>
     <t>105</t>
   </si>
   <si>
-    <t>COVID-19 MODERNA - SPIKEVAX BIVALENTE</t>
-  </si>
-  <si>
-    <t>Vacina COVID-19-RNAm, Moderna (Spikevax) bivalente</t>
+    <t>COVID-19-SPIKEVAX BI</t>
+  </si>
+  <si>
+    <t>vacina covid-19-RNAm, Moderna (Spikevax) bivalente</t>
   </si>
   <si>
     <t>106</t>
@@ -1099,7 +1099,7 @@
     <t>VPC15</t>
   </si>
   <si>
-    <t>Vacina adsorvida pneumocócica 15-valente (conjugada, polissacarídica)</t>
+    <t>vacina pneumo 15</t>
   </si>
   <si>
     <t>107</t>
@@ -1108,7 +1108,7 @@
     <t>VPC20</t>
   </si>
   <si>
-    <t>Vacina Pneumo 20</t>
+    <t>vacina pneumo 20</t>
   </si>
   <si>
     <t>108</t>
@@ -1117,7 +1117,7 @@
     <t>VVSR-Rec</t>
   </si>
   <si>
-    <t>Vacina Vírus Sincicial Respiratório A e B (recombinante)</t>
+    <t>vacina vírus sincicial respiratório A e B (recombinante)</t>
   </si>
   <si>
     <t>109</t>
@@ -1126,7 +1126,7 @@
     <t>VVSR-RecAdj</t>
   </si>
   <si>
-    <t>Vacina Vírus Sincicial Respiratório (recombinante, adjuvada)</t>
+    <t>vacina vírus sincicial respiratório (recombinante, adjuvada)</t>
   </si>
   <si>
     <t>110</t>
@@ -1135,7 +1135,7 @@
     <t>INF4-alta dosagem</t>
   </si>
   <si>
-    <t>Vacina Influenza Tetravalente - Alta Dosagem</t>
+    <t>vacina influenza tetravalente - alta dosagem</t>
   </si>
   <si>
     <t>111</t>
@@ -1144,7 +1144,7 @@
     <t>dTpa/VIP</t>
   </si>
   <si>
-    <t>Vacina Tetra Acelular dTpa/VIP</t>
+    <t>vacina tetra acelular dTpa/VIP</t>
   </si>
   <si>
     <t>112</t>
@@ -1153,7 +1153,61 @@
     <t>COVID-19 SERUM/ZALIKA</t>
   </si>
   <si>
-    <t>Vacina Covid-19-recombinante, Serum/Zalika</t>
+    <t>vacina covid-19-recombinante, Serum/Zalika</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>CHIKUNGUNYA</t>
+  </si>
+  <si>
+    <t>vacina chikungunya (recombinante e atenuada)</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>COVID-19 SINOPHARM</t>
+  </si>
+  <si>
+    <t>vacina covid-19-inativada, Sinopharm</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>NIRSEVIMABE 0,5ml</t>
+  </si>
+  <si>
+    <t>nirsevimabe 0,5ml</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>NIRSEVIMABE 1,0ml</t>
+  </si>
+  <si>
+    <t>nirsevimabe 1,0ml</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>INF3-alta dosagem</t>
+  </si>
+  <si>
+    <t>vacina influenza trivalente - alta dosagem</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>DILMenACWY</t>
+  </si>
+  <si>
+    <t>diluente para vacina meningo ACWY</t>
   </si>
 </sst>
 </file>
@@ -1461,7 +1515,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1480,14 +1534,40 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" t="s" s="2">
         <v>39</v>
       </c>
-      <c r="B2" t="s" s="2">
+      <c r="D2" t="s" s="2">
         <v>40</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" t="s" s="2">
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
         <v>41</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="C4" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1497,1306 +1577,1306 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D113"/>
+  <dimension ref="A1:D119"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>36</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="D38" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="D40" t="s" s="2">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D42" t="s" s="2">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D43" t="s" s="2">
-        <v>170</v>
+        <v>175</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="D44" t="s" s="2">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>179</v>
+        <v>184</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D47" t="s" s="2">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D48" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D49" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="D53" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="D54" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="D56" t="s" s="2">
-        <v>209</v>
+        <v>214</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="D57" t="s" s="2">
-        <v>212</v>
+        <v>217</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="D58" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="D59" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D60" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D61" t="s" s="2">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="D62" t="s" s="2">
-        <v>227</v>
+        <v>232</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="D63" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="D64" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="D66" t="s" s="2">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D67" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="D68" t="s" s="2">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>247</v>
+        <v>228</v>
       </c>
       <c r="D69" t="s" s="2">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D70" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D71" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D72" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>258</v>
+        <v>180</v>
       </c>
       <c r="D73" t="s" s="2">
-        <v>259</v>
+        <v>181</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>261</v>
+        <v>216</v>
       </c>
       <c r="D74" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D75" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D76" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D77" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D78" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D79" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D80" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D81" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D82" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D83" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D84" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D85" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D86" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D87" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D88" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D89" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D90" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D91" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D92" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>318</v>
+        <v>159</v>
       </c>
       <c r="D93" t="s" s="2">
         <v>319</v>
@@ -2804,7 +2884,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>320</v>
@@ -2818,7 +2898,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>323</v>
@@ -2832,7 +2912,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>326</v>
@@ -2846,7 +2926,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>329</v>
@@ -2860,7 +2940,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>332</v>
@@ -2874,7 +2954,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>335</v>
@@ -2888,7 +2968,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>338</v>
@@ -2902,7 +2982,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>341</v>
@@ -2916,7 +2996,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>344</v>
@@ -2930,7 +3010,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>347</v>
@@ -2944,7 +3024,7 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>350</v>
@@ -2958,7 +3038,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>353</v>
@@ -2972,7 +3052,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>356</v>
@@ -2986,7 +3066,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>359</v>
@@ -3000,7 +3080,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>362</v>
@@ -3014,7 +3094,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>365</v>
@@ -3028,7 +3108,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>368</v>
@@ -3042,7 +3122,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>371</v>
@@ -3056,7 +3136,7 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>374</v>
@@ -3070,7 +3150,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>377</v>
@@ -3080,6 +3160,90 @@
       </c>
       <c r="D113" t="s" s="2">
         <v>379</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="C114" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="D114" t="s" s="2">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="C115" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="D115" t="s" s="2">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="C116" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="D116" t="s" s="2">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="C117" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="D117" t="s" s="2">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="C118" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="D118" t="s" s="2">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="C119" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="D119" t="s" s="2">
+        <v>397</v>
       </c>
     </row>
   </sheetData>
